--- a/DateBase/orders/Dang Nguyen48_2026-10-13.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-10-13.xlsx
@@ -529,6 +529,9 @@
       <c r="A11" t="str">
         <v>6</v>
       </c>
+      <c r="C11" t="str">
+        <v>572_乒乓菊白_undefined_undefined_1bunch</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>

--- a/DateBase/orders/Dang Nguyen48_2026-10-13.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-10-13.xlsx
@@ -532,6 +532,9 @@
       <c r="C11" t="str">
         <v>572_乒乓菊白_undefined_undefined_1bunch</v>
       </c>
+      <c r="F11" t="str">
+        <v>25</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -590,7 +593,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>010020515102015250</v>
+        <v>0100205151020152525</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen48_2026-10-13.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-10-13.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:L31"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -536,9 +536,188 @@
         <v>25</v>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>7</v>
+      </c>
+      <c r="C12" t="str">
+        <v>572_乒乓菊白_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F12" t="str">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>8</v>
+      </c>
+      <c r="C13" t="str">
+        <v>734_乒乓菊红_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F13" t="str">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>9</v>
+      </c>
+      <c r="C14" t="str">
+        <v>734_乒乓菊红_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F14" t="str">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>10</v>
+      </c>
+      <c r="C15" t="str">
+        <v>175_火灵鸟_Free Spirit_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F15" t="str">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="C16" t="str">
+        <v>705_中华桔梗紫_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F16" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="C17" t="str">
+        <v>819_中华桔梗白_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F17" t="str">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="C18" t="str">
+        <v>819_中华桔梗白_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F18" t="str">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="C19" t="str">
+        <v>457_茴香花_lace flower yellow_undefined_1bunch</v>
+      </c>
+      <c r="F19" t="str">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>11</v>
+      </c>
+      <c r="C20" t="str">
+        <v>138_卡罗拉_Carola_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F20" t="str">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="C21" t="str">
+        <v>384_奶油向日葵_sunflower cream_undefined_1bunch</v>
+      </c>
+      <c r="F21" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="C22" t="str">
+        <v>383_油画向日葵_sunflower black_undefined_1bunch</v>
+      </c>
+      <c r="F22" t="str">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>12</v>
+      </c>
+      <c r="C23" t="str">
+        <v>383_油画向日葵_sunflower black_undefined_1bunch</v>
+      </c>
+      <c r="F23" t="str">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="C24" t="str">
+        <v>478_绿芯向日葵_sunflower mini_undefined_1bunch</v>
+      </c>
+      <c r="F24" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="C25" t="str">
+        <v>300_白星_White Gypso_ gypsophila_1kg</v>
+      </c>
+      <c r="F25" t="str">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="C26" t="str">
+        <v>771_美洲茶_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F26" t="str">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="27" xml:space="preserve">
+      <c r="C27" t="str" xml:space="preserve">
+        <v xml:space="preserve">497_小飞燕粉色_delphinium ballkleid
+pink_undefined_1bunch</v>
+      </c>
+      <c r="F27" t="str">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>13</v>
+      </c>
+      <c r="C28" t="str">
+        <v>831_多丁粉星太子_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F28" t="str">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="C29" t="str">
+        <v>628_多丁白星太子_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F29" t="str">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="C30" t="str">
+        <v>628_多丁白星太子_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F30" t="str">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>14</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L11"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L31"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -593,7 +772,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>0100205151020152525</v>
+        <v>01002051510201525252525273210202120301064102030202020200</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen48_2026-10-13.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-10-13.xlsx
@@ -712,7 +712,7 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>14</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen48_2026-10-13.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-10-13.xlsx
@@ -712,7 +712,7 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>1</v>
+        <v/>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen48_2026-10-13.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-10-13.xlsx
@@ -710,9 +710,13 @@
         <v>20</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" xml:space="preserve">
       <c r="A31" t="str">
         <v/>
+      </c>
+      <c r="C31" t="str" xml:space="preserve">
+        <v xml:space="preserve">373_龙柳_Salix
+_undefined_1bunch</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen48_2026-10-13.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-10-13.xlsx
@@ -718,6 +718,9 @@
         <v xml:space="preserve">373_龙柳_Salix
 _undefined_1bunch</v>
       </c>
+      <c r="F31" t="str">
+        <v>5</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -776,7 +779,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>01002051510201525252525273210202120301064102030202020200</v>
+        <v>01002051510201525252525273210202120301064102030202020205</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen48_2026-10-13.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-10-13.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L31"/>
+  <dimension ref="A1:L11"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -440,59 +440,55 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="C2" t="str">
-        <v>636_干花大叶白_undefined_undefined_1stem</v>
+        <v>571_大飞燕浅紫_undefined_undefined_1bunch</v>
       </c>
       <c r="F2" t="str">
-        <v>100</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="str">
-        <v>2</v>
-      </c>
       <c r="C3" t="str">
-        <v>882_乒乓菊黄_undefined_undefined_1bunch</v>
+        <v>402_大飞燕深紫色_delphinium purple_undefined_1bunch</v>
       </c>
       <c r="F3" t="str">
-        <v>20</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4">
       <c r="C4" t="str">
-        <v>747_乒乓菊绿_undefined_undefined_1bunch</v>
+        <v>403_大飞燕浅蓝色_delphinium light blue_undefined_1bunch</v>
       </c>
       <c r="F4" t="str">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>3</v>
-      </c>
-      <c r="C5" t="str">
-        <v>747_乒乓菊绿_undefined_undefined_1bunch</v>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="5" xml:space="preserve">
+      <c r="C5" t="str" xml:space="preserve">
+        <v xml:space="preserve">499_小飞燕浅蓝_delphinium ballkleid
+light blue_undefined_1bunch</v>
       </c>
       <c r="F5" t="str">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="C6" t="str">
-        <v>573_乒乓菊粉_undefined_undefined_1bunch</v>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6" xml:space="preserve">
+      <c r="C6" t="str" xml:space="preserve">
+        <v xml:space="preserve">405_小飞燕深蓝_ delphinium ballkleid
+dark blue_undefined_1bunch</v>
       </c>
       <c r="F6" t="str">
-        <v>10</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="C7" t="str">
-        <v>573_乒乓菊粉_undefined_undefined_1bunch</v>
+        <v>550_蕾丝红色_lace flower brown_undefined_1bunch</v>
       </c>
       <c r="F7" t="str">
         <v>20</v>
@@ -500,231 +496,36 @@
     </row>
     <row r="8">
       <c r="C8" t="str">
-        <v>734_乒乓菊红_undefined_undefined_1bunch</v>
+        <v>319_尤加利叶带果_Eucalyptus leaves with small pods_undefined_1bunch</v>
       </c>
       <c r="F8" t="str">
-        <v>1</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9">
       <c r="C9" t="str">
-        <v>734_乒乓菊红_undefined_undefined_1bunch</v>
+        <v>496_大飞燕深蓝色_delphinium dark blue_undefined_1bunch</v>
       </c>
       <c r="F9" t="str">
-        <v>5</v>
+        <v>20</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="str">
-        <v>5</v>
-      </c>
       <c r="C10" t="str">
-        <v>734_乒乓菊红_undefined_undefined_1bunch</v>
+        <v>401_大飞燕白色_delphinium white_undefined_1bunch</v>
       </c>
       <c r="F10" t="str">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="str">
-        <v>6</v>
-      </c>
       <c r="C11" t="str">
-        <v>572_乒乓菊白_undefined_undefined_1bunch</v>
-      </c>
-      <c r="F11" t="str">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>7</v>
-      </c>
-      <c r="C12" t="str">
-        <v>572_乒乓菊白_undefined_undefined_1bunch</v>
-      </c>
-      <c r="F12" t="str">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>8</v>
-      </c>
-      <c r="C13" t="str">
-        <v>734_乒乓菊红_undefined_undefined_1bunch</v>
-      </c>
-      <c r="F13" t="str">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>9</v>
-      </c>
-      <c r="C14" t="str">
-        <v>734_乒乓菊红_undefined_undefined_1bunch</v>
-      </c>
-      <c r="F14" t="str">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>10</v>
-      </c>
-      <c r="C15" t="str">
-        <v>175_火灵鸟_Free Spirit_Rosa rugosa Thunb._20stems</v>
-      </c>
-      <c r="F15" t="str">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="C16" t="str">
-        <v>705_中华桔梗紫_undefined_undefined_1bunch</v>
-      </c>
-      <c r="F16" t="str">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="C17" t="str">
-        <v>819_中华桔梗白_undefined_undefined_1bunch</v>
-      </c>
-      <c r="F17" t="str">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="C18" t="str">
-        <v>819_中华桔梗白_undefined_undefined_1bunch</v>
-      </c>
-      <c r="F18" t="str">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="C19" t="str">
-        <v>457_茴香花_lace flower yellow_undefined_1bunch</v>
-      </c>
-      <c r="F19" t="str">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="str">
-        <v>11</v>
-      </c>
-      <c r="C20" t="str">
-        <v>138_卡罗拉_Carola_Rosa rugosa Thunb._20stems</v>
-      </c>
-      <c r="F20" t="str">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="C21" t="str">
-        <v>384_奶油向日葵_sunflower cream_undefined_1bunch</v>
-      </c>
-      <c r="F21" t="str">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="C22" t="str">
-        <v>383_油画向日葵_sunflower black_undefined_1bunch</v>
-      </c>
-      <c r="F22" t="str">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="str">
-        <v>12</v>
-      </c>
-      <c r="C23" t="str">
-        <v>383_油画向日葵_sunflower black_undefined_1bunch</v>
-      </c>
-      <c r="F23" t="str">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="C24" t="str">
-        <v>478_绿芯向日葵_sunflower mini_undefined_1bunch</v>
-      </c>
-      <c r="F24" t="str">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="C25" t="str">
-        <v>300_白星_White Gypso_ gypsophila_1kg</v>
-      </c>
-      <c r="F25" t="str">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="C26" t="str">
-        <v>771_美洲茶_undefined_undefined_1bunch</v>
-      </c>
-      <c r="F26" t="str">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="27" xml:space="preserve">
-      <c r="C27" t="str" xml:space="preserve">
-        <v xml:space="preserve">497_小飞燕粉色_delphinium ballkleid
-pink_undefined_1bunch</v>
-      </c>
-      <c r="F27" t="str">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="str">
-        <v>13</v>
-      </c>
-      <c r="C28" t="str">
-        <v>831_多丁粉星太子_undefined_undefined_1bunch</v>
-      </c>
-      <c r="F28" t="str">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="C29" t="str">
-        <v>628_多丁白星太子_undefined_undefined_1bunch</v>
-      </c>
-      <c r="F29" t="str">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="C30" t="str">
-        <v>628_多丁白星太子_undefined_undefined_1bunch</v>
-      </c>
-      <c r="F30" t="str">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="31" xml:space="preserve">
-      <c r="A31" t="str">
-        <v/>
-      </c>
-      <c r="C31" t="str" xml:space="preserve">
-        <v xml:space="preserve">373_龙柳_Salix
-_undefined_1bunch</v>
-      </c>
-      <c r="F31" t="str">
-        <v>5</v>
+        <v>495_大飞燕深粉色_delphinium pink_undefined_1bunch</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L31"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L11"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -779,7 +580,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>01002051510201525252525273210202120301064102030202020205</v>
+        <v>02010302020202020200</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen48_2026-10-13.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-10-13.xlsx
@@ -522,6 +522,9 @@
       <c r="C11" t="str">
         <v>495_大飞燕深粉色_delphinium pink_undefined_1bunch</v>
       </c>
+      <c r="F11" t="str">
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -580,7 +583,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>02010302020202020200</v>
+        <v>02010302020202020201</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen48_2026-10-13.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-10-13.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:L14"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -526,9 +526,36 @@
         <v>1</v>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>15</v>
+      </c>
+      <c r="C12" t="str">
+        <v>653_大丽花 黑_undefined_undefined_5stems</v>
+      </c>
+      <c r="F12" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="C13" t="str">
+        <v>669_大丽花 红_undefined_undefined_5stems</v>
+      </c>
+      <c r="F13" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="C14" t="str">
+        <v>447_黄金球_craspedia_undefined_1bunch</v>
+      </c>
+      <c r="F14" t="str">
+        <v>20</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L11"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L14"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -583,7 +610,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>02010302020202020201</v>
+        <v>02010302020202020201151020</v>
       </c>
     </row>
   </sheetData>
